--- a/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,45</t>
+          <t>0,0; 49,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,39</t>
+          <t>0,0; 64,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,13</t>
+          <t>0,0; 40,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>0,0; 23,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,77</t>
+          <t>0,0; 26,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,27</t>
+          <t>0,0; 22,04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,66</t>
+          <t>0,0; 25,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,47</t>
+          <t>0,0; 27,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,1</t>
+          <t>0,0; 19,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,11</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,11</t>
+          <t>0,0; 50,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,37</t>
+          <t>0,0; 37,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 31,33</t>
+          <t>4,04; 31,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,69</t>
+          <t>0,0; 78,84</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,1</t>
+          <t>0,0; 48,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,99</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,76</t>
+          <t>0,0; 47,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,55</t>
+          <t>0,0; 49,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,04</t>
+          <t>0,0; 43,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,41</t>
+          <t>0,0; 22,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,01</t>
+          <t>0,0; 33,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 27,79</t>
+          <t>3,26; 26,47</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,83</t>
+          <t>0,0; 42,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 20,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,46</t>
+          <t>0,0; 71,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,27</t>
+          <t>0,0; 41,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,88</t>
+          <t>0,0; 38,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,31</t>
+          <t>0,0; 40,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,29</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,48</t>
+          <t>0,0; 22,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,62</t>
+          <t>0,0; 55,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,29</t>
+          <t>0,0; 36,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,02</t>
+          <t>0,0; 30,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 35,26</t>
+          <t>4,87; 39,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,3</t>
+          <t>0,0; 41,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,36</t>
+          <t>0,0; 32,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 36,19</t>
+          <t>6,65; 33,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 31,28</t>
+          <t>3,54; 29,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 23,3</t>
+          <t>2,62; 22,19</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,65</t>
+          <t>2,95; 16,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,9</t>
+          <t>2,72; 15,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,97</t>
+          <t>2,58; 13,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,09</t>
+          <t>1,78; 15,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,86</t>
+          <t>5,07; 17,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,22</t>
+          <t>1,46; 13,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,07</t>
+          <t>3,53; 12,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,84</t>
+          <t>4,83; 13,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,64</t>
+          <t>3,15; 10,96</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2853</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3740</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3152</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3443</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4255</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2652</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3862</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3216</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4075</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2754</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1355</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>619; 4749</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2763</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3443</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3163</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4166</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3331</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4988</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>636; 5168</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2722</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3025</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3613</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4280</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2913</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2919</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4638</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2954</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3214</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2537</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4179</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>677; 5440</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4290</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3366</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1310; 6636</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>610; 5121</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>624; 5290</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7435</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1665; 9378</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1420; 7590</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>830; 7190</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3225; 11208</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>699; 6273</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3197; 11372</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>6027; 16679</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3241; 11283</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,81</t>
+          <t>0,0; 51,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,29</t>
+          <t>0,0; 64,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,8</t>
+          <t>0,0; 41,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,14</t>
+          <t>0,0; 24,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,14</t>
+          <t>0,0; 39,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,04</t>
+          <t>0,0; 22,16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,73</t>
+          <t>0,0; 31,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,77</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,94</t>
+          <t>0,0; 20,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 14,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,8</t>
+          <t>0,0; 51,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,83</t>
+          <t>0,0; 38,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 31,04</t>
+          <t>4,12; 31,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,15</t>
+          <t>0,0; 46,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,98</t>
+          <t>0,0; 40,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,31</t>
+          <t>0,0; 41,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,8</t>
+          <t>0,0; 54,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,03</t>
+          <t>0,0; 44,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,78</t>
+          <t>0,0; 25,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,5</t>
+          <t>0,0; 30,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 26,47</t>
+          <t>3,25; 28,01</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,73</t>
+          <t>0,0; 44,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,49</t>
+          <t>0,0; 27,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,75</t>
+          <t>0,0; 71,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,72</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,48</t>
+          <t>0,0; 38,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,78</t>
+          <t>0,0; 40,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 25,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,38</t>
+          <t>0,0; 22,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,38</t>
+          <t>0,0; 55,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,87</t>
+          <t>0,0; 36,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,82</t>
+          <t>0,0; 30,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 39,16</t>
+          <t>4,92; 34,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,44</t>
+          <t>0,0; 43,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,74</t>
+          <t>0,0; 39,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,65; 33,69</t>
+          <t>6,84; 34,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 29,72</t>
+          <t>3,58; 29,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 22,19</t>
+          <t>2,61; 23,61</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,95</t>
+          <t>2,99; 17,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,3</t>
+          <t>2,54; 16,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,77</t>
+          <t>2,4; 14,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,39</t>
+          <t>1,53; 14,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,63</t>
+          <t>4,91; 17,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,11</t>
+          <t>1,45; 13,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,55</t>
+          <t>3,57; 12,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,36</t>
+          <t>5,06; 13,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,96</t>
+          <t>2,81; 10,86</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2853</t>
+          <t>0; 2931</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3152</t>
+          <t>0; 3370</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3443</t>
+          <t>0; 5253</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4278</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2652</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 3849</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3216</t>
+          <t>0; 3243</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 3758</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4075</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>619; 4749</t>
+          <t>630; 4785</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2355,42 +2355,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3443</t>
+          <t>0; 4019</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>0; 3428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>0; 3449</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>0; 3756</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4988</t>
+          <t>0; 4474</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>636; 5168</t>
+          <t>634; 5469</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2722</t>
+          <t>0; 2815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3025</t>
+          <t>0; 4030</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3613</t>
+          <t>0; 3596</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4280</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2913</t>
+          <t>0; 2896</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2919</t>
+          <t>0; 2865</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4638</t>
+          <t>0; 2921</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2954</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3214</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2537</t>
+          <t>0; 2540</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>677; 5440</t>
+          <t>683; 4823</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1310; 6636</t>
+          <t>1348; 6775</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>610; 5121</t>
+          <t>617; 5056</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>624; 5290</t>
+          <t>623; 5628</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1294; 7435</t>
+          <t>1310; 7500</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1665; 9378</t>
+          <t>1559; 9850</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1420; 7590</t>
+          <t>1321; 8031</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>830; 7190</t>
+          <t>713; 6839</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3225; 11208</t>
+          <t>3124; 10867</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>699; 6273</t>
+          <t>692; 6592</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3197; 11372</t>
+          <t>3234; 11278</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6027; 16679</t>
+          <t>6323; 17173</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3241; 11283</t>
+          <t>2894; 11188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,87%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,33%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 65,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,74</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,88</t>
+          <t>0,0; 30,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,16</t>
+          <t>0,0; 20,27</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,11</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,43</t>
+          <t>0,0; 15,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,45</t>
+          <t>0,0; 38,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,59</t>
+          <t>0,0; 50,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 31,27</t>
+          <t>4,09; 31,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,84</t>
+          <t>0,0; 78,69</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,74</t>
+          <t>0,0; 47,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,83</t>
+          <t>0,0; 44,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,29</t>
+          <t>0,0; 44,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,07</t>
+          <t>0,0; 36,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,68</t>
+          <t>0,0; 24,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,05</t>
+          <t>0,0; 33,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 28,01</t>
+          <t>3,25; 27,79</t>
         </is>
       </c>
     </row>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,31</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 71,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,76</t>
+          <t>0,0; 41,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,79%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,15</t>
+          <t>0,0; 25,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,58</t>
+          <t>0,0; 27,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,4</t>
+          <t>4,86; 35,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,92</t>
+          <t>0,0; 36,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,52</t>
+          <t>0,0; 37,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 34,71</t>
+          <t>0,0; 61,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,31</t>
+          <t>0,0; 39,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,57</t>
+          <t>0,0; 30,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 34,4</t>
+          <t>6,79; 36,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 29,34</t>
+          <t>3,57; 31,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 23,61</t>
+          <t>2,57; 23,3</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,09</t>
+          <t>1,5; 15,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,07</t>
+          <t>4,19; 16,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,57</t>
+          <t>1,4; 14,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,64</t>
+          <t>2,91; 16,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 17,1</t>
+          <t>2,48; 13,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,77</t>
+          <t>1,54; 12,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,45</t>
+          <t>3,64; 12,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,76</t>
+          <t>4,84; 12,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,86</t>
+          <t>2,74; 11,64</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1313</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2931</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3809</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3234</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3370</t>
+          <t>0; 3006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5253</t>
+          <t>0; 4053</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4278</t>
+          <t>0; 3914</t>
         </is>
       </c>
     </row>
@@ -1918,27 +1918,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3820</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3243</t>
+          <t>0; 2596</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2086,27 +2086,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1311</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4128</t>
+          <t>0; 2793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2809</t>
+          <t>0; 4019</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1355</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>630; 4785</t>
+          <t>626; 4795</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2763</t>
+          <t>0; 2757</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>832</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>824</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 3020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 4264</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3449</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4267</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3756</t>
+          <t>0; 3570</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4474</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>634; 5469</t>
+          <t>634; 5425</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4030</t>
+          <t>0; 3345</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3598</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3596</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4284</t>
+          <t>0; 4233</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,27 +2733,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>701</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2896</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2865</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2886</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2921</t>
+          <t>0; 2937</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2980</t>
+          <t>0; 3627</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1409</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1469</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>676; 4898</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2540</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>683; 4823</t>
+          <t>0; 3576</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4484</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 4071</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1348; 6775</t>
+          <t>1338; 7128</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>617; 5056</t>
+          <t>616; 5390</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>623; 5628</t>
+          <t>613; 5556</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>4335</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3546</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1310; 7500</t>
+          <t>702; 7047</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1559; 9850</t>
+          <t>2662; 10719</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1321; 8031</t>
+          <t>669; 6806</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>713; 6839</t>
+          <t>1276; 7306</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3124; 10867</t>
+          <t>1521; 8522</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>692; 6592</t>
+          <t>846; 7152</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3234; 11278</t>
+          <t>3294; 10930</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6323; 17173</t>
+          <t>6044; 16026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2894; 11188</t>
+          <t>2825; 11984</t>
         </is>
       </c>
     </row>
